--- a/site/exports/fdu-chinese.xlsx
+++ b/site/exports/fdu-chinese.xlsx
@@ -872,7 +872,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L4" s="2" t="b">
